--- a/premiacao/Inscrição de Equipe - Game Jam IFPA-PGM 2026  (respostas).xlsx
+++ b/premiacao/Inscrição de Equipe - Game Jam IFPA-PGM 2026  (respostas).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arikl\OneDrive\Área de Trabalho\GameJam2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arikl\OneDrive\Área de Trabalho\GameJam2026\premiacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83EB532-2107-45F4-8FED-EA4E715717F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237392F1-5A39-4BF3-BEFA-963C3735EA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respostas ao formulário 1" sheetId="1" r:id="rId1"/>
@@ -955,15 +955,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1049,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000665E5733}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1086,7 +1086,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00006559571A}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1123,7 +1123,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000074A9025D}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1385,10 +1385,10 @@
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="37" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="29.7109375" customWidth="1"/>
     <col min="10" max="10" width="31.7109375" customWidth="1"/>
@@ -3253,16 +3253,16 @@
     </row>
     <row r="2" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -3509,16 +3509,16 @@
     </row>
     <row r="8" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -3717,16 +3717,16 @@
     </row>
     <row r="13" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -3885,16 +3885,16 @@
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="5" t="s">
@@ -4093,16 +4093,16 @@
     </row>
     <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="21" t="s">
         <v>75</v>
       </c>
       <c r="F22" s="5" t="s">
@@ -4221,16 +4221,16 @@
     </row>
     <row r="25" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
@@ -4477,16 +4477,16 @@
     </row>
     <row r="31" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="21" t="s">
         <v>95</v>
       </c>
       <c r="F31" s="5" t="s">
@@ -4565,16 +4565,16 @@
     </row>
     <row r="33" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="5" t="s">
@@ -4693,16 +4693,16 @@
     </row>
     <row r="36" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="5" t="s">
@@ -4901,16 +4901,16 @@
     </row>
     <row r="41" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="21" t="s">
         <v>31</v>
       </c>
       <c r="F41" s="5" t="s">
@@ -5109,16 +5109,16 @@
     </row>
     <row r="46" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="5" t="s">
@@ -5317,16 +5317,16 @@
     </row>
     <row r="51" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="5" t="s">
@@ -5493,16 +5493,16 @@
     </row>
     <row r="55" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="5" t="s">
@@ -5701,16 +5701,16 @@
     </row>
     <row r="60" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -5909,16 +5909,16 @@
     </row>
     <row r="65" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="5" t="s">
@@ -5997,16 +5997,16 @@
     </row>
     <row r="67" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="5" t="s">
@@ -6205,16 +6205,16 @@
     </row>
     <row r="72" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="21" t="s">
         <v>179</v>
       </c>
       <c r="F72" s="5" t="s">
@@ -6333,16 +6333,16 @@
     </row>
     <row r="75" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C75" s="21" t="s">
+      <c r="C75" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="5" t="s">
@@ -6461,16 +6461,16 @@
     </row>
     <row r="78" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="5" t="s">
@@ -6629,16 +6629,16 @@
     </row>
     <row r="82" spans="1:32" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
-      <c r="B82" s="20" t="s">
+      <c r="B82" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="5" t="s">
@@ -37364,22 +37364,54 @@
   </sheetData>
   <autoFilter ref="A1:AF85" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="D36:D40"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="D41:D45"/>
-    <mergeCell ref="E41:E45"/>
-    <mergeCell ref="B41:B45"/>
-    <mergeCell ref="B46:B50"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="D46:D50"/>
-    <mergeCell ref="E46:E50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="D25:D29"/>
+    <mergeCell ref="E25:E29"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D75:D77"/>
+    <mergeCell ref="E75:E77"/>
+    <mergeCell ref="B75:B77"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="C55:C59"/>
     <mergeCell ref="D55:D59"/>
@@ -37396,54 +37428,22 @@
     <mergeCell ref="C60:C64"/>
     <mergeCell ref="D60:D64"/>
     <mergeCell ref="E60:E64"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="C75:C77"/>
-    <mergeCell ref="D75:D77"/>
-    <mergeCell ref="E75:E77"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="C25:C29"/>
-    <mergeCell ref="D25:D29"/>
-    <mergeCell ref="E25:E29"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="B25:B29"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="D46:D50"/>
+    <mergeCell ref="E46:E50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="D36:D40"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="D41:D45"/>
+    <mergeCell ref="E41:E45"/>
+    <mergeCell ref="B41:B45"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
